--- a/data/trans_orig/IP21B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP21B-Edad-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29897</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8632</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>64,77%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55247</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20661</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>11431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>48,44%</t>
         </is>
       </c>
     </row>
@@ -3136,47 +3136,47 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>4892</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10238</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7989</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>5054</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10232</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7989</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29476</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45377</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54722</t>
+          <t>54682</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>36659</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,95%</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP21B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP21B-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3561</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>719</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3585</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3637</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3573</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15650</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12808</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17658</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15650</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12784</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>16369</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,61%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>78,1%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>17658</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>17658</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>17658</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16369</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16369</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5817</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1289</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3266</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3241</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>32,98%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>83,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>728</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5378</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,05%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8637</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>3908</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>67,02%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6628</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8614</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,95%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>42,43%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,21%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9342</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9342</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9342</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>3908</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>3908</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>3908</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>9342</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9342</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,74 +1409,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1181</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>1959</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>60,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2699</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>57,35%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>57,59%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4071</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>1959</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4071</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,49%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>42,65%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1959</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>1959</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>1959</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1887</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>1887</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>1887</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>1887</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7603</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2469</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,72%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7536</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29085</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25551</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31733</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>22942</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20129</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24828</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19900</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24773</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,28%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29085</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>25618</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>31277</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47552</t>
+          <t>47395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55249</t>
+          <t>55417</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>25411</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2012 (tasa de respuesta: 97,75%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2012 (tasa de respuesta: 97,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,107 +2670,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1379</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4588</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,59%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1379</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4844</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13008</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9799</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10215</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>14387</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,41%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>71,0%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10614</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>34</t>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14387</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>14387</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>14387</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8081</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>63,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2974</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6068</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5816</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>27,13%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>55,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4650</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7585</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>36,79%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11431</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,79%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7989</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10630</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>36,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,1%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>7986</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4892</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10238</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10236</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,87%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7989</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5054</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>10694</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>63,21%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12639</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12639</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12639</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>10960</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>10960</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>10960</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>12639</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>12639</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>12639</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3469,47 +3469,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1343</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3887</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1343</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>1343</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>1343</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3887</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3887</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3887</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,107 +3699,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3177</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>59,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1205</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3257</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>18,06%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>61,72%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3266</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>18,06%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4132</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2160</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>40,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1336</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4132</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5337</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>38,28%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>1336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>1336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>1336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>5337</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>5337</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>5337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,21%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4353</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8175</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8427</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2687</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9777</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26623</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22341</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29847</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>23673</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19851</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26467</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19599</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26563</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>84,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>70,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26623</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>22700</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>29790</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>81,97%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45114</t>
+          <t>45223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>28026</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>28026</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>28026</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6777</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5803</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6777</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>6777</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>6777</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5803</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5803</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5803</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2686</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>40,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3280</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1259</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5355</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>46,64%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1316</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2681</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>40,27%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>59,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>3752</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1677</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5773</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1819</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5778</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>53,36%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>59,73%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>79,63%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>7032</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>7032</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>7032</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3941</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>74,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1497</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3486</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3497</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>36,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>85,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2186</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3909</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -5421,69 +5421,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4668</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>2570</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>4067</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>63,19%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4729</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>58,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>25,9%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4067</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4067</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>4067</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5276</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5276</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5276</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,107 +5646,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3504</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>891</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>59,9%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>9,19%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5458</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2845</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3352</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5458</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2546</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6349</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>40,1%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>3352</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>3352</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>3352</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>6349</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>6349</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>6349</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8458</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4777</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8692</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8479</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1597</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8186</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>19055</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>78,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16451</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>12536</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>19071</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12749</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>19139</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>77,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>59,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>16303</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>12511</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>19100</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>78,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36659</t>
+          <t>36809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>21228</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2701</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>73,66%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3704</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>36,45%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3673</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>39,11%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2258</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,04%</t>
         </is>
       </c>
     </row>
@@ -7025,27 +7025,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7060,27 +7060,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>743</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>627</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -7438,27 +7438,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,107 +7593,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1756</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3775</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4043</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>34,52%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3823</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>32,88%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -7711,69 +7711,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3775</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>56,16%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6332</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4782</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8326</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10448</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6972</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4433</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8602</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>75,66%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
